--- a/Advanced Reactor Materials/Fall2026/presentation_grading.xlsx
+++ b/Advanced Reactor Materials/Fall2026/presentation_grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5992A4-5A42-3C44-B0EA-49A51AA702CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A4D8A9-8E8A-9644-B6E7-90F0B12BDB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24620" yWindow="9220" windowWidth="26040" windowHeight="17180" xr2:uid="{86373935-D16D-7E49-AE9B-FB508A32B91B}"/>
+    <workbookView xWindow="5060" yWindow="6780" windowWidth="26040" windowHeight="17180" xr2:uid="{86373935-D16D-7E49-AE9B-FB508A32B91B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -722,11 +722,11 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <f t="shared" ref="D16:F16" si="0">2*D11+D12+D13</f>
+        <f>2*D11+D12+D13</f>
         <v>73</v>
       </c>
       <c r="E16">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D16:F16" si="0">2*E11+E12+E13</f>
         <v>69</v>
       </c>
       <c r="F16">
